--- a/SOA-C03/SOA-C03-ExamTopics-Questions.xlsx
+++ b/SOA-C03/SOA-C03-ExamTopics-Questions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jetstarairways-my.sharepoint.com/personal/balraj_singh_jetstar_com/Documents/Balraj_D_Laptop_Drive/DevOps_Master/Learn-AI-MCP_ML/SOA-C03/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MY_DevOps_Journey\AWS-Exam-Certificate-Preparation\SOA-C03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="584" documentId="8_{6D7FEDCE-BF68-490E-8FEE-13CF0653E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1D2C752-F2BF-4E30-8616-AFA9E65B6DDD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2050B9B5-3A98-45AE-8407-7BBF50932252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{D730D107-BEC6-4E62-9FED-4CE422768F8C}"/>
   </bookViews>
   <sheets>
     <sheet name="ExamTopics" sheetId="4" r:id="rId1"/>
@@ -587,7 +587,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -699,17 +699,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -727,16 +717,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1102,14 +1082,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA114F14-55CB-4CDF-A972-40E7E00E52B4}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:E241"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
@@ -1118,7 +1098,7 @@
       </c>
       <c r="D1" s="7"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="B2" s="2" t="str">
         <f>TEXT(COUNTIF(B5:B242,"Yes")/COUNTA(B5:B242),"0.00%")</f>
         <v>70.97%</v>
@@ -1136,7 +1116,7 @@
         <v>88.78%</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1157,7 +1137,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1195,7 +1175,7 @@
         <v>2092026</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1209,7 +1189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -1223,7 +1203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" hidden="1">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1237,7 +1217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" hidden="1">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1251,7 +1231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -1265,7 +1245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -1279,7 +1259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -1293,7 +1273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" hidden="1">
       <c r="A13" s="1">
         <v>8</v>
       </c>
@@ -1307,7 +1287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" hidden="1">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -1321,7 +1301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -1335,7 +1315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1">
       <c r="A16" s="1">
         <v>11</v>
       </c>
@@ -1349,7 +1329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1">
       <c r="A17" s="1">
         <v>12</v>
       </c>
@@ -1363,7 +1343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" hidden="1">
       <c r="A18" s="1">
         <v>13</v>
       </c>
@@ -1377,7 +1357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" hidden="1">
       <c r="A19" s="1">
         <v>14</v>
       </c>
@@ -1391,7 +1371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -1405,7 +1385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" hidden="1">
       <c r="A21" s="1">
         <v>16</v>
       </c>
@@ -1419,7 +1399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1">
       <c r="A22" s="1">
         <v>17</v>
       </c>
@@ -1433,7 +1413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1">
       <c r="A23" s="1">
         <v>18</v>
       </c>
@@ -1447,7 +1427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" hidden="1">
       <c r="A24" s="1">
         <v>19</v>
       </c>
@@ -1461,7 +1441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" hidden="1">
       <c r="A25" s="1">
         <v>20</v>
       </c>
@@ -1475,7 +1455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" hidden="1">
       <c r="A26" s="1">
         <v>21</v>
       </c>
@@ -1489,7 +1469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" hidden="1">
       <c r="A27" s="1">
         <v>22</v>
       </c>
@@ -1503,7 +1483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" hidden="1">
       <c r="A28" s="1">
         <v>23</v>
       </c>
@@ -1517,7 +1497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" hidden="1">
       <c r="A29" s="1">
         <v>24</v>
       </c>
@@ -1531,7 +1511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" hidden="1">
       <c r="A30" s="1">
         <v>25</v>
       </c>
@@ -1545,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" hidden="1">
       <c r="A31" s="1">
         <v>26</v>
       </c>
@@ -1559,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" hidden="1">
       <c r="A32" s="1">
         <v>27</v>
       </c>
@@ -1573,7 +1553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" hidden="1">
       <c r="A33" s="1">
         <v>28</v>
       </c>
@@ -1587,7 +1567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" hidden="1">
       <c r="A34" s="1">
         <v>29</v>
       </c>
@@ -1601,7 +1581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" hidden="1">
       <c r="A35" s="1">
         <v>30</v>
       </c>
@@ -1615,7 +1595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" hidden="1">
       <c r="A36" s="1">
         <v>31</v>
       </c>
@@ -1626,7 +1606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" hidden="1">
       <c r="A37" s="1">
         <v>32</v>
       </c>
@@ -1637,7 +1617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" hidden="1">
       <c r="A38" s="1">
         <v>33</v>
       </c>
@@ -1648,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" hidden="1">
       <c r="A39" s="1">
         <v>34</v>
       </c>
@@ -1659,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" hidden="1">
       <c r="A40" s="1">
         <v>35</v>
       </c>
@@ -1670,7 +1650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" hidden="1">
       <c r="A41" s="1">
         <v>36</v>
       </c>
@@ -1681,7 +1661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" hidden="1">
       <c r="A42" s="1">
         <v>37</v>
       </c>
@@ -1692,7 +1672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" hidden="1">
       <c r="A43" s="1">
         <v>38</v>
       </c>
@@ -1703,7 +1683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" hidden="1">
       <c r="A44" s="1">
         <v>39</v>
       </c>
@@ -1714,7 +1694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" hidden="1">
       <c r="A45" s="1">
         <v>40</v>
       </c>
@@ -1725,7 +1705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1">
       <c r="A46" s="1">
         <v>41</v>
       </c>
@@ -1736,7 +1716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1">
       <c r="A47" s="1">
         <v>42</v>
       </c>
@@ -1747,7 +1727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1">
       <c r="A48" s="1">
         <v>43</v>
       </c>
@@ -1758,7 +1738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1">
       <c r="A49" s="1">
         <v>44</v>
       </c>
@@ -1769,7 +1749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1">
       <c r="A50" s="1">
         <v>45</v>
       </c>
@@ -1780,7 +1760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1">
       <c r="A51" s="1">
         <v>46</v>
       </c>
@@ -1791,7 +1771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1">
       <c r="A52" s="1">
         <v>47</v>
       </c>
@@ -1802,7 +1782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1">
       <c r="A53" s="1">
         <v>48</v>
       </c>
@@ -1813,7 +1793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1">
       <c r="A54" s="1">
         <v>49</v>
       </c>
@@ -1824,7 +1804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1">
       <c r="A55" s="1">
         <v>50</v>
       </c>
@@ -1835,7 +1815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1">
       <c r="A56" s="1">
         <v>51</v>
       </c>
@@ -1846,7 +1826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1">
       <c r="A57" s="1">
         <v>52</v>
       </c>
@@ -1857,7 +1837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1">
       <c r="A58" s="1">
         <v>53</v>
       </c>
@@ -1868,7 +1848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1">
       <c r="A59" s="1">
         <v>54</v>
       </c>
@@ -1879,7 +1859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1">
       <c r="A60" s="1">
         <v>55</v>
       </c>
@@ -1890,7 +1870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1">
       <c r="A61" s="1">
         <v>56</v>
       </c>
@@ -1901,7 +1881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1">
       <c r="A62" s="1">
         <v>57</v>
       </c>
@@ -1912,7 +1892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1">
       <c r="A63" s="1">
         <v>58</v>
       </c>
@@ -1923,7 +1903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1">
       <c r="A64" s="1">
         <v>59</v>
       </c>
@@ -1934,7 +1914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1">
       <c r="A65" s="1">
         <v>60</v>
       </c>
@@ -1945,7 +1925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1">
       <c r="A66" s="1">
         <v>61</v>
       </c>
@@ -1956,7 +1936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1">
       <c r="A67" s="1">
         <v>62</v>
       </c>
@@ -1967,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1">
       <c r="A68" s="1">
         <v>63</v>
       </c>
@@ -1978,7 +1958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1">
       <c r="A69" s="1">
         <v>64</v>
       </c>
@@ -1989,7 +1969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1">
       <c r="A70" s="1">
         <v>65</v>
       </c>
@@ -2000,7 +1980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1">
       <c r="A71" s="1">
         <v>66</v>
       </c>
@@ -2011,7 +1991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1">
       <c r="A72" s="1">
         <v>67</v>
       </c>
@@ -2022,7 +2002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1">
       <c r="A73" s="1">
         <v>68</v>
       </c>
@@ -2033,7 +2013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1">
       <c r="A74" s="1">
         <v>69</v>
       </c>
@@ -2044,7 +2024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1">
       <c r="A75" s="1">
         <v>70</v>
       </c>
@@ -2055,7 +2035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1">
       <c r="A76" s="1">
         <v>71</v>
       </c>
@@ -2066,7 +2046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1">
       <c r="A77" s="1">
         <v>72</v>
       </c>
@@ -2077,7 +2057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1">
       <c r="A78" s="1">
         <v>73</v>
       </c>
@@ -2088,7 +2068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1">
       <c r="A79" s="1">
         <v>74</v>
       </c>
@@ -2099,7 +2079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1">
       <c r="A80" s="1">
         <v>75</v>
       </c>
@@ -2110,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1">
       <c r="A81" s="1">
         <v>76</v>
       </c>
@@ -2121,7 +2101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1">
       <c r="A82" s="1">
         <v>77</v>
       </c>
@@ -2132,7 +2112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1">
       <c r="A83" s="1">
         <v>78</v>
       </c>
@@ -2143,7 +2123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1">
       <c r="A84" s="1">
         <v>79</v>
       </c>
@@ -2154,7 +2134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1">
       <c r="A85" s="1">
         <v>80</v>
       </c>
@@ -2165,7 +2145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5">
       <c r="A86" s="1">
         <v>81</v>
       </c>
@@ -2176,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5">
       <c r="A87" s="1">
         <v>82</v>
       </c>
@@ -2187,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1">
       <c r="A88" s="1">
         <v>83</v>
       </c>
@@ -2198,7 +2178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1">
       <c r="A89" s="1">
         <v>84</v>
       </c>
@@ -2209,7 +2189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1">
       <c r="A90" s="1">
         <v>85</v>
       </c>
@@ -2220,7 +2200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1">
       <c r="A91" s="1">
         <v>86</v>
       </c>
@@ -2231,7 +2211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1">
       <c r="A92" s="1">
         <v>87</v>
       </c>
@@ -2242,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5">
       <c r="A93" s="1">
         <v>88</v>
       </c>
@@ -2253,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1">
       <c r="A94" s="1">
         <v>89</v>
       </c>
@@ -2264,7 +2244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5">
       <c r="A95" s="1">
         <v>90</v>
       </c>
@@ -2275,7 +2255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1">
       <c r="A96" s="1">
         <v>91</v>
       </c>
@@ -2286,7 +2266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1">
       <c r="A97" s="1">
         <v>92</v>
       </c>
@@ -2297,7 +2277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5">
       <c r="A98" s="1">
         <v>93</v>
       </c>
@@ -2308,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1">
       <c r="A99" s="1">
         <v>94</v>
       </c>
@@ -2319,7 +2299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1">
       <c r="A100" s="1">
         <v>95</v>
       </c>
@@ -2330,7 +2310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1">
       <c r="A101" s="1">
         <v>96</v>
       </c>
@@ -2341,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5">
       <c r="A102" s="1">
         <v>97</v>
       </c>
@@ -2352,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1">
       <c r="A103" s="1">
         <v>98</v>
       </c>
@@ -2363,7 +2343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1">
       <c r="A104" s="1">
         <v>99</v>
       </c>
@@ -2374,7 +2354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1">
       <c r="A105" s="1">
         <v>100</v>
       </c>
@@ -2385,7 +2365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1">
       <c r="A106" s="1">
         <v>101</v>
       </c>
@@ -2393,7 +2373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1">
       <c r="A107" s="1">
         <v>102</v>
       </c>
@@ -2401,7 +2381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108" s="1">
         <v>103</v>
       </c>
@@ -2409,7 +2389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1">
       <c r="A109" s="1">
         <v>104</v>
       </c>
@@ -2417,7 +2397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1">
       <c r="A110" s="1">
         <v>105</v>
       </c>
@@ -2425,7 +2405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1">
       <c r="A111" s="1">
         <v>106</v>
       </c>
@@ -2433,7 +2413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1">
       <c r="A112" s="1">
         <v>107</v>
       </c>
@@ -2441,7 +2421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1">
       <c r="A113" s="1">
         <v>108</v>
       </c>
@@ -2449,7 +2429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5">
       <c r="A114" s="1">
         <v>109</v>
       </c>
@@ -2457,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1">
       <c r="A115" s="1">
         <v>110</v>
       </c>
@@ -2465,7 +2445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1">
       <c r="A116" s="1">
         <v>111</v>
       </c>
@@ -2473,7 +2453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1">
       <c r="A117" s="1">
         <v>112</v>
       </c>
@@ -2481,7 +2461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1">
       <c r="A118" s="1">
         <v>113</v>
       </c>
@@ -2489,7 +2469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1">
       <c r="A119" s="1">
         <v>114</v>
       </c>
@@ -2497,7 +2477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1">
       <c r="A120" s="1">
         <v>115</v>
       </c>
@@ -2505,7 +2485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1">
       <c r="A121" s="1">
         <v>116</v>
       </c>
@@ -2513,7 +2493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" hidden="1">
       <c r="A122" s="1">
         <v>117</v>
       </c>
@@ -2521,7 +2501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" hidden="1">
       <c r="A123" s="1">
         <v>118</v>
       </c>
@@ -2529,7 +2509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5">
       <c r="A124" s="1">
         <v>119</v>
       </c>
@@ -2537,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" hidden="1">
       <c r="A125" s="1">
         <v>120</v>
       </c>
@@ -2545,7 +2525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" hidden="1">
       <c r="A126" s="1">
         <v>121</v>
       </c>
@@ -2553,7 +2533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" hidden="1">
       <c r="A127" s="1">
         <v>122</v>
       </c>
@@ -2561,7 +2541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" hidden="1">
       <c r="A128" s="1">
         <v>123</v>
       </c>
@@ -2569,7 +2549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5">
       <c r="A129" s="1">
         <v>124</v>
       </c>
@@ -2577,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" hidden="1">
       <c r="A130" s="1">
         <v>125</v>
       </c>
@@ -2585,7 +2565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" hidden="1">
       <c r="A131" s="1">
         <v>126</v>
       </c>
@@ -2593,7 +2573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5">
       <c r="A132" s="1">
         <v>127</v>
       </c>
@@ -2601,7 +2581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" hidden="1">
       <c r="A133" s="1">
         <v>128</v>
       </c>
@@ -2609,7 +2589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" hidden="1">
       <c r="A134" s="1">
         <v>129</v>
       </c>
@@ -2617,7 +2597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5">
       <c r="A135" s="1">
         <v>130</v>
       </c>
@@ -2625,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" hidden="1">
       <c r="A136" s="1">
         <v>131</v>
       </c>
@@ -2633,7 +2613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5">
       <c r="A137" s="1">
         <v>132</v>
       </c>
@@ -2641,7 +2621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" hidden="1">
       <c r="A138" s="1">
         <v>133</v>
       </c>
@@ -2649,7 +2629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" hidden="1">
       <c r="A139" s="1">
         <v>134</v>
       </c>
@@ -2657,7 +2637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5">
       <c r="A140" s="1">
         <v>135</v>
       </c>
@@ -2665,7 +2645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" hidden="1">
       <c r="A141" s="1">
         <v>136</v>
       </c>
@@ -2673,7 +2653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" hidden="1">
       <c r="A142" s="1">
         <v>137</v>
       </c>
@@ -2681,7 +2661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" hidden="1">
       <c r="A143" s="1">
         <v>138</v>
       </c>
@@ -2689,7 +2669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5">
       <c r="A144" s="1">
         <v>139</v>
       </c>
@@ -2697,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" hidden="1">
       <c r="A145" s="1">
         <v>140</v>
       </c>
@@ -2705,7 +2685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" hidden="1">
       <c r="A146" s="1">
         <v>141</v>
       </c>
@@ -2713,7 +2693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" hidden="1">
       <c r="A147" s="1">
         <v>142</v>
       </c>
@@ -2721,7 +2701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" hidden="1">
       <c r="A148" s="1">
         <v>143</v>
       </c>
@@ -2729,7 +2709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" hidden="1">
       <c r="A149" s="1">
         <v>144</v>
       </c>
@@ -2737,7 +2717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" hidden="1">
       <c r="A150" s="1">
         <v>145</v>
       </c>
@@ -2745,7 +2725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" hidden="1">
       <c r="A151" s="1">
         <v>146</v>
       </c>
@@ -2753,7 +2733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" hidden="1">
       <c r="A152" s="1">
         <v>147</v>
       </c>
@@ -2761,7 +2741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" hidden="1">
       <c r="A153" s="1">
         <v>148</v>
       </c>
@@ -2769,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" hidden="1">
       <c r="A154" s="1">
         <v>149</v>
       </c>
@@ -2777,7 +2757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" hidden="1">
       <c r="A155" s="1">
         <v>150</v>
       </c>
@@ -2785,7 +2765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" hidden="1">
       <c r="A156" s="1">
         <v>151</v>
       </c>
@@ -2793,7 +2773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" hidden="1">
       <c r="A157" s="1">
         <v>152</v>
       </c>
@@ -2801,7 +2781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" hidden="1">
       <c r="A158" s="1">
         <v>153</v>
       </c>
@@ -2809,7 +2789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" hidden="1">
       <c r="A159" s="1">
         <v>154</v>
       </c>
@@ -2817,7 +2797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" hidden="1">
       <c r="A160" s="1">
         <v>155</v>
       </c>
@@ -2825,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5">
       <c r="A161" s="1">
         <v>156</v>
       </c>
@@ -2833,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" hidden="1">
       <c r="A162" s="1">
         <v>157</v>
       </c>
@@ -2841,7 +2821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" hidden="1">
       <c r="A163" s="1">
         <v>158</v>
       </c>
@@ -2849,7 +2829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5">
       <c r="A164" s="1">
         <v>159</v>
       </c>
@@ -2857,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" hidden="1">
       <c r="A165" s="1">
         <v>160</v>
       </c>
@@ -2865,7 +2845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" hidden="1">
       <c r="A166" s="1">
         <v>161</v>
       </c>
@@ -2873,7 +2853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5">
       <c r="A167" s="1">
         <v>162</v>
       </c>
@@ -2881,7 +2861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" hidden="1">
       <c r="A168" s="1">
         <v>163</v>
       </c>
@@ -2889,7 +2869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" hidden="1">
       <c r="A169" s="1">
         <v>164</v>
       </c>
@@ -2897,7 +2877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" hidden="1">
       <c r="A170" s="1">
         <v>165</v>
       </c>
@@ -2905,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" hidden="1">
       <c r="A171" s="1">
         <v>166</v>
       </c>
@@ -2913,7 +2893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" hidden="1">
       <c r="A172" s="1">
         <v>167</v>
       </c>
@@ -2921,7 +2901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" hidden="1">
       <c r="A173" s="1">
         <v>168</v>
       </c>
@@ -2929,7 +2909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" hidden="1">
       <c r="A174" s="1">
         <v>169</v>
       </c>
@@ -2937,7 +2917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" hidden="1">
       <c r="A175" s="1">
         <v>170</v>
       </c>
@@ -2945,7 +2925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" hidden="1">
       <c r="A176" s="1">
         <v>171</v>
       </c>
@@ -2953,7 +2933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" hidden="1">
       <c r="A177" s="1">
         <v>172</v>
       </c>
@@ -2961,7 +2941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5">
       <c r="A178" s="1">
         <v>173</v>
       </c>
@@ -2969,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" hidden="1">
       <c r="A179" s="1">
         <v>174</v>
       </c>
@@ -2977,7 +2957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" hidden="1">
       <c r="A180" s="1">
         <v>175</v>
       </c>
@@ -2985,7 +2965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" hidden="1">
       <c r="A181" s="1">
         <v>176</v>
       </c>
@@ -2993,7 +2973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" hidden="1">
       <c r="A182" s="1">
         <v>177</v>
       </c>
@@ -3001,7 +2981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" hidden="1">
       <c r="A183" s="1">
         <v>178</v>
       </c>
@@ -3009,7 +2989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" hidden="1">
       <c r="A184" s="1">
         <v>179</v>
       </c>
@@ -3017,7 +2997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" hidden="1">
       <c r="A185" s="1">
         <v>180</v>
       </c>
@@ -3025,7 +3005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" hidden="1">
       <c r="A186" s="1">
         <v>181</v>
       </c>
@@ -3033,7 +3013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" hidden="1">
       <c r="A187" s="1">
         <v>182</v>
       </c>
@@ -3041,7 +3021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5">
       <c r="A188" s="1">
         <v>183</v>
       </c>
@@ -3049,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" hidden="1">
       <c r="A189" s="1">
         <v>184</v>
       </c>
@@ -3057,7 +3037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" hidden="1">
       <c r="A190" s="1">
         <v>185</v>
       </c>
@@ -3065,7 +3045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5">
       <c r="A191" s="1">
         <v>186</v>
       </c>
@@ -3073,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" hidden="1">
       <c r="A192" s="1">
         <v>187</v>
       </c>
@@ -3081,7 +3061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" hidden="1">
       <c r="A193" s="1">
         <v>188</v>
       </c>
@@ -3089,7 +3069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" hidden="1">
       <c r="A194" s="1">
         <v>189</v>
       </c>
@@ -3097,7 +3077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" hidden="1">
       <c r="A195" s="1">
         <v>190</v>
       </c>
@@ -3105,7 +3085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" hidden="1">
       <c r="A196" s="1">
         <v>191</v>
       </c>
@@ -3113,7 +3093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" hidden="1">
       <c r="A197" s="1">
         <v>192</v>
       </c>
@@ -3121,7 +3101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" hidden="1">
       <c r="A198" s="1">
         <v>193</v>
       </c>
@@ -3129,7 +3109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" hidden="1">
       <c r="A199" s="1">
         <v>194</v>
       </c>
@@ -3137,7 +3117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" hidden="1">
       <c r="A200" s="1">
         <v>195</v>
       </c>
@@ -3145,207 +3125,207 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" hidden="1">
       <c r="A201" s="1">
         <v>196</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" hidden="1">
       <c r="A202" s="1">
         <v>197</v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" hidden="1">
       <c r="A203" s="1">
         <v>198</v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" hidden="1">
       <c r="A204" s="1">
         <v>199</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" hidden="1">
       <c r="A205" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" hidden="1">
       <c r="A206" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" hidden="1">
       <c r="A207" s="1">
         <v>202</v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" hidden="1">
       <c r="A208" s="1">
         <v>203</v>
       </c>
     </row>
-    <row r="209" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:1" hidden="1">
       <c r="A209" s="1">
         <v>204</v>
       </c>
     </row>
-    <row r="210" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:1" hidden="1">
       <c r="A210" s="1">
         <v>205</v>
       </c>
     </row>
-    <row r="211" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:1" hidden="1">
       <c r="A211" s="1">
         <v>206</v>
       </c>
     </row>
-    <row r="212" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:1" hidden="1">
       <c r="A212" s="1">
         <v>207</v>
       </c>
     </row>
-    <row r="213" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:1" hidden="1">
       <c r="A213" s="1">
         <v>208</v>
       </c>
     </row>
-    <row r="214" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:1" hidden="1">
       <c r="A214" s="1">
         <v>209</v>
       </c>
     </row>
-    <row r="215" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:1" hidden="1">
       <c r="A215" s="1">
         <v>210</v>
       </c>
     </row>
-    <row r="216" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:1" hidden="1">
       <c r="A216" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="217" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:1" hidden="1">
       <c r="A217" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="218" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:1" hidden="1">
       <c r="A218" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="219" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:1" hidden="1">
       <c r="A219" s="1">
         <v>214</v>
       </c>
     </row>
-    <row r="220" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:1" hidden="1">
       <c r="A220" s="1">
         <v>215</v>
       </c>
     </row>
-    <row r="221" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:1" hidden="1">
       <c r="A221" s="1">
         <v>216</v>
       </c>
     </row>
-    <row r="222" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:1" hidden="1">
       <c r="A222" s="1">
         <v>217</v>
       </c>
     </row>
-    <row r="223" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:1" hidden="1">
       <c r="A223" s="1">
         <v>218</v>
       </c>
     </row>
-    <row r="224" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:1" hidden="1">
       <c r="A224" s="1">
         <v>219</v>
       </c>
     </row>
-    <row r="225" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:1" hidden="1">
       <c r="A225" s="1">
         <v>220</v>
       </c>
     </row>
-    <row r="226" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:1" hidden="1">
       <c r="A226" s="1">
         <v>221</v>
       </c>
     </row>
-    <row r="227" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:1" hidden="1">
       <c r="A227" s="1">
         <v>222</v>
       </c>
     </row>
-    <row r="228" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:1" hidden="1">
       <c r="A228" s="1">
         <v>223</v>
       </c>
     </row>
-    <row r="229" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:1" hidden="1">
       <c r="A229" s="1">
         <v>224</v>
       </c>
     </row>
-    <row r="230" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:1" hidden="1">
       <c r="A230" s="1">
         <v>225</v>
       </c>
     </row>
-    <row r="231" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:1" hidden="1">
       <c r="A231" s="1">
         <v>226</v>
       </c>
     </row>
-    <row r="232" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:1" hidden="1">
       <c r="A232" s="1">
         <v>227</v>
       </c>
     </row>
-    <row r="233" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:1" hidden="1">
       <c r="A233" s="1">
         <v>228</v>
       </c>
     </row>
-    <row r="234" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:1" hidden="1">
       <c r="A234" s="1">
         <v>229</v>
       </c>
     </row>
-    <row r="235" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:1" hidden="1">
       <c r="A235" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="236" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:1" hidden="1">
       <c r="A236" s="1">
         <v>231</v>
       </c>
     </row>
-    <row r="237" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:1" hidden="1">
       <c r="A237" s="1">
         <v>232</v>
       </c>
     </row>
-    <row r="238" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:1" hidden="1">
       <c r="A238" s="1">
         <v>233</v>
       </c>
     </row>
-    <row r="239" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:1" hidden="1">
       <c r="A239" s="1">
         <v>234</v>
       </c>
     </row>
-    <row r="240" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:1" hidden="1">
       <c r="A240" s="1">
         <v>235</v>
       </c>
     </row>
-    <row r="241" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:1" hidden="1">
       <c r="A241" s="1">
         <v>236</v>
       </c>
@@ -3359,18 +3339,18 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="C6:C75 B6:B1048576 D76:D105">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",B6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",B6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E200">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",E6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",E6)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3381,15 +3361,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E3CCDD-CECD-4B29-8FAC-EFB87C60FE25}">
   <dimension ref="A1:Z202"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="108.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="108.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="2" bestFit="1" customWidth="1"/>
     <col min="7" max="21" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26">
       <c r="A1" s="8" t="s">
         <v>179</v>
       </c>
@@ -3469,7 +3449,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3477,7 +3457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3485,7 +3465,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3493,7 +3473,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3501,7 +3481,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3509,7 +3489,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3517,7 +3497,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3525,7 +3505,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3533,7 +3513,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3541,7 +3521,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3549,7 +3529,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3557,7 +3537,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3565,7 +3545,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3573,7 +3553,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3581,7 +3561,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3589,7 +3569,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3597,7 +3577,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3605,7 +3585,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3613,7 +3593,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3621,7 +3601,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3629,7 +3609,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3637,7 +3617,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3645,7 +3625,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3653,7 +3633,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3661,7 +3641,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3669,7 +3649,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3677,7 +3657,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3685,7 +3665,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3693,7 +3673,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3701,7 +3681,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3709,7 +3689,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3717,7 +3697,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3725,7 +3705,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3733,7 +3713,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3741,7 +3721,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3749,7 +3729,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3757,7 +3737,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3765,7 +3745,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3773,7 +3753,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -3781,7 +3761,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -3789,7 +3769,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -3797,7 +3777,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -3805,7 +3785,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -3813,7 +3793,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -3821,7 +3801,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -3829,7 +3809,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -3837,7 +3817,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -3845,7 +3825,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -3853,7 +3833,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -3861,7 +3841,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -3869,7 +3849,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -3877,7 +3857,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -3885,7 +3865,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -3893,7 +3873,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -3901,7 +3881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -3909,7 +3889,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -3917,7 +3897,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -3925,7 +3905,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -3933,7 +3913,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -3941,7 +3921,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -3949,7 +3929,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -3957,7 +3937,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -3965,7 +3945,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -3973,7 +3953,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -3981,7 +3961,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -3989,7 +3969,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -3997,7 +3977,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -4005,7 +3985,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -4013,7 +3993,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -4021,7 +4001,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -4029,7 +4009,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4037,7 +4017,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4045,7 +4025,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4053,7 +4033,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4061,7 +4041,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4069,7 +4049,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4077,7 +4057,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4085,7 +4065,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4093,7 +4073,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4101,7 +4081,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4109,7 +4089,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4117,7 +4097,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4125,7 +4105,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4133,7 +4113,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4141,7 +4121,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4149,7 +4129,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -4157,7 +4137,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -4165,7 +4145,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -4173,7 +4153,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -4181,12 +4161,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2">
       <c r="A91" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -4194,7 +4174,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -4202,12 +4182,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2">
       <c r="A94" s="1">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -4215,7 +4195,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -4223,7 +4203,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -4231,12 +4211,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2">
       <c r="A98" s="1">
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -4244,7 +4224,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -4252,12 +4232,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2">
       <c r="A101" s="1">
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -4265,7 +4245,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -4273,12 +4253,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2">
       <c r="A104" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -4286,12 +4266,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2">
       <c r="A106" s="1">
         <v>104</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -4299,7 +4279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -4307,12 +4287,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2">
       <c r="A109" s="1">
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -4320,7 +4300,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -4328,7 +4308,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -4336,7 +4316,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -4344,12 +4324,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2">
       <c r="A114" s="1">
         <v>112</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -4357,7 +4337,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -4365,12 +4345,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2">
       <c r="A117" s="1">
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -4378,12 +4358,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2">
       <c r="A119" s="1">
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -4391,7 +4371,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -4399,12 +4379,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2">
       <c r="A122" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -4412,12 +4392,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2">
       <c r="A124" s="1">
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -4425,7 +4405,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -4433,7 +4413,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -4441,7 +4421,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -4449,7 +4429,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -4457,7 +4437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -4465,7 +4445,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -4473,7 +4453,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -4481,7 +4461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -4489,7 +4469,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -4497,7 +4477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -4505,7 +4485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -4513,7 +4493,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -4521,7 +4501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -4529,7 +4509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -4537,7 +4517,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -4545,7 +4525,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -4553,7 +4533,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -4561,7 +4541,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -4569,7 +4549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -4577,7 +4557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -4585,7 +4565,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -4593,12 +4573,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2">
       <c r="A147" s="1">
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -4606,12 +4586,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2">
       <c r="A149" s="1">
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -4619,7 +4599,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -4627,7 +4607,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -4635,7 +4615,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -4643,7 +4623,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -4651,7 +4631,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -4659,7 +4639,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -4667,7 +4647,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -4675,7 +4655,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -4683,7 +4663,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -4691,7 +4671,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -4699,7 +4679,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -4707,7 +4687,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -4715,7 +4695,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -4723,7 +4703,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -4731,7 +4711,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -4739,7 +4719,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -4747,7 +4727,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -4755,7 +4735,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -4763,7 +4743,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -4771,7 +4751,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -4779,12 +4759,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2">
       <c r="A171" s="1">
         <v>169</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -4792,7 +4772,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -4800,7 +4780,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -4808,7 +4788,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -4816,12 +4796,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2">
       <c r="A176" s="1">
         <v>174</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -4829,7 +4809,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -4837,7 +4817,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -4845,7 +4825,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -4853,12 +4833,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2">
       <c r="A181" s="1">
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -4866,7 +4846,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -4874,7 +4854,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -4882,7 +4862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -4890,7 +4870,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -4898,12 +4878,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2">
       <c r="A187" s="1">
         <v>185</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -4911,7 +4891,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -4919,7 +4899,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -4927,7 +4907,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -4935,12 +4915,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2">
       <c r="A192" s="1">
         <v>190</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -4948,7 +4928,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -4956,7 +4936,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -4964,7 +4944,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -4972,12 +4952,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2">
       <c r="A197" s="1">
         <v>195</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -4985,7 +4965,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -4993,7 +4973,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -5001,7 +4981,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -5009,7 +4989,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -5020,7 +5000,7 @@
   </sheetData>
   <autoFilter ref="A2:S202" xr:uid="{44E3CCDD-CECD-4B29-8FAC-EFB87C60FE25}"/>
   <conditionalFormatting sqref="B2:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{E4BE23F5-8686-4318-92B6-7D7B715CDD5E}"/>
